--- a/rulex-ui/public/dummy_file.xlsx
+++ b/rulex-ui/public/dummy_file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\RuleX\rulex-ui\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52598C5D-D754-4E02-9027-5096A170F21E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{608CBEFA-023C-415E-8FA1-F9389D93A930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,12 +25,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="4">
   <si>
     <t>Name</t>
   </si>
   <si>
     <t>AAA</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>ww</t>
   </si>
 </sst>
 </file>
@@ -352,6 +358,7 @@
   <dimension ref="A1:F28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -359,143 +366,227 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
+      <c r="B2" s="1">
+        <v>44602</v>
+      </c>
       <c r="F2" s="1"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
+      <c r="B3" s="1">
+        <v>44603</v>
+      </c>
       <c r="F3" s="1"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>1</v>
       </c>
+      <c r="B4" s="1">
+        <v>44604</v>
+      </c>
       <c r="F4" s="1"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>1</v>
       </c>
+      <c r="B5" s="1">
+        <v>44605</v>
+      </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>1</v>
       </c>
+      <c r="B6" s="1">
+        <v>44606</v>
+      </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>1</v>
       </c>
+      <c r="B7" s="1">
+        <v>44607</v>
+      </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>1</v>
       </c>
+      <c r="B8" s="1">
+        <v>44608</v>
+      </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>1</v>
       </c>
+      <c r="B9" s="1">
+        <v>44609</v>
+      </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>1</v>
       </c>
+      <c r="B10" s="1">
+        <v>44610</v>
+      </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>1</v>
       </c>
+      <c r="B11" s="1">
+        <v>44611</v>
+      </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>1</v>
       </c>
+      <c r="B12" s="1">
+        <v>44612</v>
+      </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>1</v>
       </c>
+      <c r="B13" s="1">
+        <v>44613</v>
+      </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>1</v>
       </c>
+      <c r="B14" s="1">
+        <v>44614</v>
+      </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>1</v>
+      <c r="A15">
+        <v>1</v>
+      </c>
+      <c r="B15" s="1">
+        <v>44615</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B16" s="1">
+        <v>44616</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B17" s="1">
+        <v>44617</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B18" s="1">
+        <v>44618</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B19" s="1">
+        <v>44619</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B20" s="1">
+        <v>44620</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B21" s="1">
+        <v>44621</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B22" s="1">
+        <v>44622</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B23" s="1">
+        <v>44623</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B24" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B25" s="1">
+        <v>44625</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B26" s="1">
+        <v>44626</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B27" s="1">
+        <v>44627</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>1</v>
+      </c>
+      <c r="B28" s="1">
+        <v>44628</v>
       </c>
     </row>
   </sheetData>
